--- a/data/dividends_info_20260702.xlsx
+++ b/data/dividends_info_20260702.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>61.93999862670898</v>
+        <v>61.77999877929688</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1453019082909559</v>
+        <v>0.1456782158923576</v>
       </c>
       <c r="J2" t="n">
         <v>256</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.90000152587891</v>
+        <v>65.40000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.06221545340194</v>
+        <v>1.070336366464775</v>
       </c>
       <c r="J3" t="n">
         <v>235</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.279999732971191</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I4" t="n">
-        <v>0.646551742742235</v>
+        <v>0.6479481481313648</v>
       </c>
       <c r="J4" t="n">
         <v>165</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>61.93999862670898</v>
+        <v>61.77999877929688</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1453019082909559</v>
+        <v>0.1456782158923576</v>
       </c>
       <c r="J6" t="n">
         <v>165</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20.25</v>
+        <v>20.40999984741211</v>
       </c>
       <c r="I8" t="n">
-        <v>1.333333333333333</v>
+        <v>1.322880950605371</v>
       </c>
       <c r="J8" t="n">
         <v>144</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.960000038146973</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I9" t="n">
-        <v>3.355704676508394</v>
+        <v>3.412969205515265</v>
       </c>
       <c r="J9" t="n">
         <v>137</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.849999904632568</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7643312194767268</v>
+        <v>0.7317073340929389</v>
       </c>
       <c r="J10" t="n">
         <v>109</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.980000019073486</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8361203986709481</v>
+        <v>0.8064516377126522</v>
       </c>
       <c r="J12" t="n">
         <v>95</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.989999771118164</v>
+        <v>4.940000057220459</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7615230810218038</v>
+        <v>0.7692307603207009</v>
       </c>
       <c r="J13" t="n">
         <v>88</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20.25</v>
+        <v>20.40999984741211</v>
       </c>
       <c r="I14" t="n">
-        <v>1.333333333333333</v>
+        <v>1.322880950605371</v>
       </c>
       <c r="J14" t="n">
         <v>81</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>61.93999862670898</v>
+        <v>61.77999877929688</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1453019082909559</v>
+        <v>0.1456782158923576</v>
       </c>
       <c r="J15" t="n">
         <v>81</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.960000038146973</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="I16" t="n">
-        <v>5.03355701476259</v>
+        <v>4.950495096249109</v>
       </c>
       <c r="J16" t="n">
         <v>74</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.989999771118164</v>
+        <v>4.940000057220459</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7615230810218038</v>
+        <v>0.7692307603207009</v>
       </c>
       <c r="J18" t="n">
         <v>32</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.760000228881836</v>
+        <v>5.75</v>
       </c>
       <c r="I19" t="n">
-        <v>4.340277605310641</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="J19" t="n">
         <v>25</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.139999866485596</v>
+        <v>4.150000095367432</v>
       </c>
       <c r="I20" t="n">
-        <v>3.381642621134783</v>
+        <v>3.373493898380374</v>
       </c>
       <c r="J20" t="n">
         <v>18</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.03400039672852</v>
+        <v>10.11800003051758</v>
       </c>
       <c r="I21" t="n">
-        <v>2.591189851704315</v>
+        <v>2.569677794186565</v>
       </c>
       <c r="J21" t="n">
         <v>18</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.85999965667725</v>
+        <v>14.80000019073486</v>
       </c>
       <c r="I22" t="n">
-        <v>4.037685153851224</v>
+        <v>4.05405400180747</v>
       </c>
       <c r="J22" t="n">
         <v>18</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.819999933242798</v>
+        <v>2.871999979019165</v>
       </c>
       <c r="I23" t="n">
-        <v>7.801418624397476</v>
+        <v>7.660167186879076</v>
       </c>
       <c r="J23" t="n">
         <v>18</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.860000133514404</v>
+        <v>6.880000114440918</v>
       </c>
       <c r="I25" t="n">
-        <v>1.457725919150524</v>
+        <v>1.45348834791591</v>
       </c>
       <c r="J25" t="n">
         <v>18</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19.5</v>
+        <v>19.64999961853027</v>
       </c>
       <c r="I26" t="n">
-        <v>1.928205128205128</v>
+        <v>1.91348604223598</v>
       </c>
       <c r="J26" t="n">
         <v>18</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3.019999980926514</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>4.966887448588033</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
         <v>11</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.220000028610229</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I30" t="n">
-        <v>3.828828779484834</v>
+        <v>3.761061962773576</v>
       </c>
       <c r="J30" t="n">
         <v>4</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>36.95000076293945</v>
+        <v>38.40000152587891</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4059539834988278</v>
+        <v>0.3906249844779577</v>
       </c>
       <c r="J32" t="n">
         <v>4</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.150000095367432</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7766990147433418</v>
+        <v>0.7407407276587887</v>
       </c>
       <c r="J33" t="n">
         <v>-3</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21.57999992370605</v>
+        <v>21.5</v>
       </c>
       <c r="I34" t="n">
-        <v>1.158480078238416</v>
+        <v>1.162790697674419</v>
       </c>
       <c r="J34" t="n">
         <v>-10</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>31.64999961853027</v>
+        <v>30.85000038146973</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6161137515016981</v>
+        <v>0.6320907539344089</v>
       </c>
       <c r="J35" t="n">
         <v>-10</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.210000038146973</v>
+        <v>5.255000114440918</v>
       </c>
       <c r="I37" t="n">
-        <v>5.566218769225643</v>
+        <v>5.518553638144938</v>
       </c>
       <c r="J37" t="n">
         <v>-10</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.674000024795532</v>
+        <v>3.733999967575073</v>
       </c>
       <c r="I38" t="n">
-        <v>4.354926481224083</v>
+        <v>4.284949153438448</v>
       </c>
       <c r="J38" t="n">
         <v>-10</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.467999935150146</v>
+        <v>2.5</v>
       </c>
       <c r="I39" t="n">
-        <v>5.615883453885421</v>
+        <v>5.544</v>
       </c>
       <c r="J39" t="n">
         <v>-10</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>50.72999954223633</v>
+        <v>51.93999862670898</v>
       </c>
       <c r="I40" t="n">
-        <v>1.241868727941699</v>
+        <v>1.212938037460857</v>
       </c>
       <c r="J40" t="n">
         <v>-10</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.105000019073486</v>
+        <v>6.130000114440918</v>
       </c>
       <c r="I41" t="n">
-        <v>2.293202286037779</v>
+        <v>2.283849875796758</v>
       </c>
       <c r="J41" t="n">
         <v>-10</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>16.70000076293945</v>
+        <v>16.75</v>
       </c>
       <c r="I42" t="n">
-        <v>4.670658469255712</v>
+        <v>4.656716417910448</v>
       </c>
       <c r="J42" t="n">
         <v>-10</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>29.25</v>
+        <v>29.17000007629395</v>
       </c>
       <c r="I43" t="n">
-        <v>2.905982905982906</v>
+        <v>2.91395268349959</v>
       </c>
       <c r="J43" t="n">
         <v>-10</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>61.93999862670898</v>
+        <v>61.77999877929688</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1453019082909559</v>
+        <v>0.1456782158923576</v>
       </c>
       <c r="J44" t="n">
         <v>-10</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.370000004768372</v>
+        <v>1.360000014305115</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7299270047587131</v>
+        <v>0.7352941099128922</v>
       </c>
       <c r="J45" t="n">
         <v>-10</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.23799991607666</v>
+        <v>6.265999794006348</v>
       </c>
       <c r="I46" t="n">
-        <v>2.90638028918133</v>
+        <v>2.893393009259591</v>
       </c>
       <c r="J46" t="n">
         <v>-10</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.600000381469727</v>
+        <v>9.470000267028809</v>
       </c>
       <c r="I47" t="n">
-        <v>2.70833322571384</v>
+        <v>2.745512066195268</v>
       </c>
       <c r="J47" t="n">
         <v>-10</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.15999984741211</v>
+        <v>10.21500015258789</v>
       </c>
       <c r="I48" t="n">
-        <v>2.726377993701995</v>
+        <v>2.711698442117245</v>
       </c>
       <c r="J48" t="n">
         <v>-10</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.9760000109672546</v>
+        <v>1.019999980926514</v>
       </c>
       <c r="I49" t="n">
-        <v>1.383196705768575</v>
+        <v>1.32352943651404</v>
       </c>
       <c r="J49" t="n">
         <v>-17</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.00600004196167</v>
+        <v>2.996000051498413</v>
       </c>
       <c r="I50" t="n">
-        <v>3.659347919643264</v>
+        <v>3.67156201966635</v>
       </c>
       <c r="J50" t="n">
         <v>-17</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.950000047683716</v>
+        <v>2.984999895095825</v>
       </c>
       <c r="I52" t="n">
-        <v>5.423728725890325</v>
+        <v>5.360134191725446</v>
       </c>
       <c r="J52" t="n">
         <v>-24</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.39999961853027</v>
+        <v>27.45000076293945</v>
       </c>
       <c r="I54" t="n">
-        <v>4.051094946911317</v>
+        <v>4.043715734604362</v>
       </c>
       <c r="J54" t="n">
         <v>-28</v>
@@ -2990,7 +2990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C172"/>
+  <dimension ref="A1:C141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4067,7 +4067,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4077,14 +4077,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4094,14 +4094,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4135,7 +4135,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4332,14 +4332,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4349,14 +4349,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4366,14 +4366,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4400,14 +4400,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4417,14 +4417,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4441,7 +4441,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4458,7 +4458,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4468,14 +4468,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4485,14 +4485,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4519,14 +4519,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4536,14 +4536,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4560,7 +4560,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4570,14 +4570,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4587,14 +4587,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4604,14 +4604,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4621,14 +4621,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4645,7 +4645,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4662,7 +4662,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4689,14 +4689,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4713,7 +4713,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CASTELLO SGR S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4730,7 +4730,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4740,14 +4740,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4764,7 +4764,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4781,7 +4781,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4808,14 +4808,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4876,14 +4876,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4900,7 +4900,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4917,7 +4917,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4927,14 +4927,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4985,7 +4985,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5002,7 +5002,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5012,14 +5012,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5036,7 +5036,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5070,7 +5070,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5087,7 +5087,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5097,19 +5097,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5121,80 +5121,80 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5206,12 +5206,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5223,29 +5223,29 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5257,46 +5257,46 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5308,12 +5308,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5325,12 +5325,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5342,12 +5342,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5359,12 +5359,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5376,544 +5376,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
           <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>IREN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>ENEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>ESAUTOMOTION S.p.A.</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>FinecoBank S.p.A.</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>First Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Banca Profilo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Basic Net S.p.A.</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>BIESSE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Basic Net S.p.A.</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>GREEN OLEO S.p.A</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Tinexta S.p.A.</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Svas Biosana S.p.A.</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Nusco S.p.A.</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Ferretti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>ERG S.p.A.</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>ERG S.p.A.</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>DiaSorin S.p.A</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Comer Industries S.p.A.</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Tinexta S.p.A.</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5941,61 +5414,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Confinvest Oro S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MEVIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>